--- a/data/trans_orig/P35_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54834</t>
+          <t>56126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>33310</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53977</t>
+          <t>54169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67695</t>
+          <t>70551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100933</t>
+          <t>103187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32841</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132323</t>
+          <t>132502</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175937</t>
+          <t>173215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158259</t>
+          <t>158778</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>194246</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>302784</t>
+          <t>300100</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>357366</t>
+          <t>358314</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>406452</t>
+          <t>406949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>453366</t>
+          <t>452917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>423050</t>
+          <t>424178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>462579</t>
+          <t>462833</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>841939</t>
+          <t>845900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>904277</t>
+          <t>910882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49206</t>
+          <t>44385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>123807</t>
+          <t>127060</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91134</t>
+          <t>89526</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125753</t>
+          <t>124077</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>136360</t>
+          <t>134501</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>234920</t>
+          <t>234064</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48953</t>
+          <t>47947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,82 +1427,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>37000</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>28615</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>49004</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>69523</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>44665</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>88157</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>4,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>37000</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27484</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>47624</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>69523</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>44900</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>87955</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110079</t>
+          <t>93894</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267279</t>
+          <t>266391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226791</t>
+          <t>224664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>272342</t>
+          <t>270867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303284</t>
+          <t>299680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>523401</t>
+          <t>523686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>768441</t>
+          <t>767077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1016848</t>
+          <t>1042586</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>537226</t>
+          <t>538447</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>587283</t>
+          <t>592977</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1325659</t>
+          <t>1327130</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1662180</t>
+          <t>1666632</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>51865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94033</t>
+          <t>89804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28283</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78354</t>
+          <t>78167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77259</t>
+          <t>80716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156149</t>
+          <t>153388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21626</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>37890</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>23481</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>51841</t>
+          <t>50876</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>130932</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173306</t>
+          <t>174475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86958</t>
+          <t>86248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>234225</t>
+          <t>231321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213705</t>
+          <t>218238</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>385582</t>
+          <t>381452</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>442725</t>
+          <t>442054</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498735</t>
+          <t>497168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>593722</t>
+          <t>598420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>802443</t>
+          <t>807880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1062049</t>
+          <t>1066658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1327743</t>
+          <t>1307781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35518</t>
+          <t>36656</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62361</t>
+          <t>63297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36825</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63474</t>
+          <t>63547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80088</t>
+          <t>79945</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117104</t>
+          <t>118828</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37452</t>
+          <t>36931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21866</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>43796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46277</t>
+          <t>45029</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73361</t>
+          <t>72186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>225118</t>
+          <t>224250</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>280289</t>
+          <t>278686</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>249190</t>
+          <t>247409</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>338571</t>
+          <t>339213</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>488110</t>
+          <t>489483</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>600797</t>
+          <t>598300</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>571079</t>
+          <t>570936</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>630758</t>
+          <t>628381</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>667360</t>
+          <t>665468</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>780293</t>
+          <t>781671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1254011</t>
+          <t>1256281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1388790</t>
+          <t>1390855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>197361</t>
+          <t>190888</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>291370</t>
+          <t>290477</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>204602</t>
+          <t>206715</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>286856</t>
+          <t>287427</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>431360</t>
+          <t>436537</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>558136</t>
+          <t>561352</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>63014</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103078</t>
+          <t>103445</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84247</t>
+          <t>82936</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>125935</t>
+          <t>126208</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>155565</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218111</t>
+          <t>217810</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>596184</t>
+          <t>587059</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>838612</t>
+          <t>837186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>748005</t>
+          <t>716102</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>980549</t>
+          <t>983232</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1442636</t>
+          <t>1458872</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1778575</t>
+          <t>1787915</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2254994</t>
+          <t>2261121</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2597568</t>
+          <t>2616493</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2294154</t>
+          <t>2285001</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2612763</t>
+          <t>2650351</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4606494</t>
+          <t>4585586</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5082941</t>
+          <t>5067105</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Habitat-trans_orig.xlsx
@@ -725,102 +725,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>47058</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>34159</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56126</t>
+          <t>63918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>46667</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35986</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>60011</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>93725</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>76390</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>113840</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42141</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33310</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>54169</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>84024</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>70551</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>103187</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22807</t>
+          <t>26146</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32365</t>
+          <t>38069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>151946</t>
+          <t>163438</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132502</t>
+          <t>141539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>173215</t>
+          <t>186158</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>177163</t>
+          <t>191617</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158778</t>
+          <t>172460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>195391</t>
+          <t>212381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>329109</t>
+          <t>355055</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>300100</t>
+          <t>328111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>358314</t>
+          <t>385740</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>430624</t>
+          <t>467689</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>406949</t>
+          <t>441947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>452917</t>
+          <t>491101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>443495</t>
+          <t>480046</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>424178</t>
+          <t>457372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>462833</t>
+          <t>500823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>874119</t>
+          <t>947735</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>845900</t>
+          <t>914389</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>910882</t>
+          <t>979369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>68,84%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>674618</t>
+          <t>731951</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674618</t>
+          <t>731951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674618</t>
+          <t>731951</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1310060</t>
+          <t>1422661</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1310060</t>
+          <t>1422661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1310060</t>
+          <t>1422661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90721</t>
+          <t>101255</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44385</t>
+          <t>79749</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127060</t>
+          <t>124731</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>106253</t>
+          <t>118998</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89526</t>
+          <t>101863</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124077</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>196974</t>
+          <t>220253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>134501</t>
+          <t>193106</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>234064</t>
+          <t>250600</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32523</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47947</t>
+          <t>51406</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>42628</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>32362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>55952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>69523</t>
+          <t>80113</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44665</t>
+          <t>65121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88157</t>
+          <t>98046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202487</t>
+          <t>228780</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93894</t>
+          <t>202539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>266391</t>
+          <t>260624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>249314</t>
+          <t>275514</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224664</t>
+          <t>250424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>270867</t>
+          <t>300931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>451801</t>
+          <t>504295</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299680</t>
+          <t>469449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>523686</t>
+          <t>545311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>867133</t>
+          <t>681396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>767077</t>
+          <t>644160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1042586</t>
+          <t>714168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>564997</t>
+          <t>633086</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>538447</t>
+          <t>602488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592977</t>
+          <t>660698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1432130</t>
+          <t>1314482</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1327130</t>
+          <t>1265702</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1666632</t>
+          <t>1356262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>957564</t>
+          <t>1070226</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957564</t>
+          <t>1070226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>957564</t>
+          <t>1070226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2150428</t>
+          <t>2119143</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150428</t>
+          <t>2119143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2150428</t>
+          <t>2119143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>69550</t>
+          <t>77791</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51865</t>
+          <t>58655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89804</t>
+          <t>100325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54763</t>
+          <t>69776</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>54967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78167</t>
+          <t>88069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>124313</t>
+          <t>147567</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80716</t>
+          <t>124131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153388</t>
+          <t>175145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24943</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37890</t>
+          <t>39836</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>37892</t>
+          <t>43230</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>30775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>50876</t>
+          <t>55985</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>151859</t>
+          <t>173572</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130932</t>
+          <t>149430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174475</t>
+          <t>197297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>172969</t>
+          <t>196507</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86248</t>
+          <t>175694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231321</t>
+          <t>219285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>324829</t>
+          <t>370079</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218238</t>
+          <t>340674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>381452</t>
+          <t>407882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>470321</t>
+          <t>536773</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>442054</t>
+          <t>504389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>497168</t>
+          <t>567870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>679961</t>
+          <t>516959</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>598420</t>
+          <t>491873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>807880</t>
+          <t>543623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1150283</t>
+          <t>1053732</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1066658</t>
+          <t>1012328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1307781</t>
+          <t>1091563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>932635</t>
+          <t>811536</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932635</t>
+          <t>811536</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>932635</t>
+          <t>811536</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1637316</t>
+          <t>1614609</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1637316</t>
+          <t>1614609</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1637316</t>
+          <t>1614609</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48629</t>
+          <t>59057</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36656</t>
+          <t>43658</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63297</t>
+          <t>74692</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49646</t>
+          <t>59533</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>47196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63547</t>
+          <t>75288</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>98275</t>
+          <t>118590</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79945</t>
+          <t>96338</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118828</t>
+          <t>139133</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>26509</t>
+          <t>33453</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>24043</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36931</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>35521</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>25149</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43796</t>
+          <t>46498</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>58059</t>
+          <t>68974</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45029</t>
+          <t>54243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72186</t>
+          <t>85162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>251618</t>
+          <t>265219</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>224250</t>
+          <t>237391</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>278686</t>
+          <t>293621</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>306074</t>
+          <t>334435</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>247409</t>
+          <t>310637</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>339213</t>
+          <t>361213</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>557691</t>
+          <t>599654</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>489483</t>
+          <t>559194</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>598300</t>
+          <t>638049</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>600075</t>
+          <t>632333</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>570936</t>
+          <t>601794</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>628381</t>
+          <t>662224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>704032</t>
+          <t>687481</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>665468</t>
+          <t>658375</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>781671</t>
+          <t>713517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1304108</t>
+          <t>1319813</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1256281</t>
+          <t>1276518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1390855</t>
+          <t>1370399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1091301</t>
+          <t>1116970</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1091301</t>
+          <t>1116970</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1091301</t>
+          <t>1116970</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2018133</t>
+          <t>2107032</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2018133</t>
+          <t>2107032</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2018133</t>
+          <t>2107032</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>250784</t>
+          <t>285161</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>190888</t>
+          <t>250295</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>290477</t>
+          <t>324539</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>252802</t>
+          <t>294975</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>206715</t>
+          <t>261820</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>287427</t>
+          <t>326249</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>503586</t>
+          <t>580135</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>436537</t>
+          <t>535725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>561352</t>
+          <t>636233</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>82969</t>
+          <t>98401</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63014</t>
+          <t>81195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103445</t>
+          <t>121037</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>105312</t>
+          <t>120063</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82936</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126208</t>
+          <t>140616</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>188281</t>
+          <t>218463</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>156361</t>
+          <t>191229</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>217810</t>
+          <t>245245</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>757910</t>
+          <t>831009</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>587059</t>
+          <t>781410</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>837186</t>
+          <t>883940</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>905520</t>
+          <t>998074</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>716102</t>
+          <t>955359</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>983232</t>
+          <t>1046008</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1663430</t>
+          <t>1829083</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1458872</t>
+          <t>1760189</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1787915</t>
+          <t>1898049</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2368154</t>
+          <t>2318192</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2261121</t>
+          <t>2253048</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2616493</t>
+          <t>2378110</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2392485</t>
+          <t>2317572</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2285001</t>
+          <t>2262407</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2650351</t>
+          <t>2366738</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4760640</t>
+          <t>4635764</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4585586</t>
+          <t>4546423</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5067105</t>
+          <t>4708190</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
